--- a/data/material.xlsx
+++ b/data/material.xlsx
@@ -3,15 +3,19 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12000" windowHeight="24000" activeTab="1"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Material" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="Daten" state="hidden" r:id="rId4"/>
+    <sheet sheetId="2" name="Lagerbestand" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="15">
   <si>
     <t>Kategorie</t>
   </si>
@@ -47,13 +51,22 @@
   </si>
   <si>
     <t>Meter</t>
+  </si>
+  <si>
+    <t>Lagerbestand · Horst Zienert GmbH</t>
+  </si>
+  <si>
+    <t>Materialverwaltung – Anlagenmechaniker SHK</t>
+  </si>
+  <si>
+    <t>Stand: 27.08.2026 20:54 Uhr</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -61,16 +74,54 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="FF1F3864"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF5B6B87"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF5B6B87"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF2E5395"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E5395"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8EEF7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -78,12 +129,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFB6C6E3"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -490,4 +561,142 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="46" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+    </row>
+    <row r="5" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="7">
+        <v>12</v>
+      </c>
+      <c r="C7" s="7">
+        <v>0</v>
+      </c>
+      <c r="D7" s="7">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="7">
+        <v>5</v>
+      </c>
+      <c r="C12" s="7">
+        <v>2</v>
+      </c>
+      <c r="D12" s="7">
+        <v>1</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A10:E10"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
 </file>
--- a/data/material.xlsx
+++ b/data/material.xlsx
@@ -59,7 +59,7 @@
     <t>Materialverwaltung – Anlagenmechaniker SHK</t>
   </si>
   <si>
-    <t>Stand: 27.08.2026 20:54 Uhr</t>
+    <t>Stand: 27.08.2026 21:17 Uhr</t>
   </si>
 </sst>
 </file>
